--- a/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,101 +593,101 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fBoFTriU</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1176198887759649</v>
+        <v>-1.47647207908063</v>
       </c>
       <c r="C2" t="n">
-        <v>2.245989055553462</v>
+        <v>0.1345123541393592</v>
       </c>
       <c r="D2" t="n">
-        <v>2.228836768199174</v>
+        <v>1.827660902356663</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.310825613085734</v>
+        <v>3.133458207594984</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1281737999117493</v>
+        <v>-1.662201125504612</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4903481272080951</v>
+        <v>-0.849583076661939</v>
       </c>
       <c r="H2" t="n">
-        <v>0.465572143691882</v>
+        <v>-0.370864502294484</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9174827070290748</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1031118038771009</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.21557204944385</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8399936521911291</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9304836007520274</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01117263445260765</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9685802832023551</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8088430348648575</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2975002707697693</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.198580366882543</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.86088776144392</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1589701170604376</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8947407525261463</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7517145384879123</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.322692085059381</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.743287424529852</v>
+        <v>-0.5239124094119472</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.971494520826279</v>
+        <v>-0.5336512952030967</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.2024932250294328</v>
+        <v>-0.5501919728676752</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2828154796464946</v>
+        <v>1.369901346229692</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3627430169674673</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.642512608518512</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.8510287646031446</v>
+        <v>-0.2154898269961419</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1902170125549422</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.294443501020599</v>
+        <v>-0.5576836106671057</v>
       </c>
       <c r="AG2" t="n">
         <v>-0.2192196608739769</v>
@@ -696,101 +696,101 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8EBlrr6N</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1466013704499423</v>
+        <v>0.9392651481276638</v>
       </c>
       <c r="C3" t="n">
-        <v>2.245989055553462</v>
+        <v>-1.635715587450242</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228836768199174</v>
+        <v>-0.3942362007710887</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.310825613085734</v>
+        <v>4.855600117935343</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6395162417760367</v>
+        <v>4.133013215623979</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.179617474726922</v>
+        <v>2.500244933013146</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04735382069869903</v>
+        <v>1.720227112671431</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.117167329087225</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08727737992306904</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.233306712612124</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4893045795376406</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1072684515674734</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01117263445260765</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2688811533651317</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1701772660905532</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.096512006526775</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5430309087289171</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3289060157927554</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.839318054902036</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1764180597966729</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6157881348534656</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4577312389321876</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.08893792768425891</v>
+        <v>1.099518085418156</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.3718635754244647</v>
+        <v>1.590566165167378</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4885460820998384</v>
+        <v>-0.4839789641794126</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8847515744416764</v>
+        <v>0.6377662360768745</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1580387416001338</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.9723119035627555</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.6286425047198536</v>
+        <v>0.003268937196141936</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.4029577973203566</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.6892176718165767</v>
+        <v>0.7797032608578869</v>
       </c>
       <c r="AG3" t="n">
         <v>-0.2192196608739769</v>
@@ -799,101 +799,101 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YeJyopM4</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.052502830653053</v>
+        <v>0.6750438889017567</v>
       </c>
       <c r="C4" t="n">
-        <v>2.245989055553462</v>
+        <v>1.158258633612863</v>
       </c>
       <c r="D4" t="n">
-        <v>2.228836768199174</v>
+        <v>1.117888216635298</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.310825613085734</v>
+        <v>3.133458207594984</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.366675931718903</v>
+        <v>-0.4690687611546076</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.189514280531973</v>
+        <v>-0.849583076661939</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.20730114828085</v>
+        <v>-0.370864502294484</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1249466526670462</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.826742195551896</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7364327608906214</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4893045795376407</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5520193311329739</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01117263445260765</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2688811533651317</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.375125328804906</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.04250272369280263</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.915011768610118</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3481616604905452</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7579430202379228</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2545755558410109</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.06642238838232731</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.86723303709218</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.356961122727044</v>
+        <v>-1.670424621989281</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.510698849280665</v>
+        <v>-1.507467294177631</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.2487083587472169</v>
+        <v>0.514615788485408</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.6869733060616315</v>
+        <v>-0.8785658287791878</v>
       </c>
       <c r="AB4" t="n">
-        <v>-6.37155143190073</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.642512608518512</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1032641412766732</v>
+        <v>0.01759428949813836</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.6045016986770646</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.830924753259374</v>
+        <v>-1.038657077002678</v>
       </c>
       <c r="AG4" t="n">
         <v>-0.2192196608739769</v>
@@ -902,619 +902,104 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fB7pqOjH</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.212250819854723</v>
+        <v>-0.7215541955780383</v>
       </c>
       <c r="C5" t="n">
-        <v>2.245989055553462</v>
+        <v>-0.1107601919845012</v>
       </c>
       <c r="D5" t="n">
-        <v>2.228836768199174</v>
+        <v>1.889380266332434</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.310825613085734</v>
+        <v>3.133458207594984</v>
       </c>
       <c r="F5" t="n">
-        <v>1.064958564438255</v>
+        <v>-1.150858683640324</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.179617474726922</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04735382069869903</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8552481183904999</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3670604450546092</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.765682495992656</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4893045795376406</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7822333075635275</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01117263445260765</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3824143395651242</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.110080050543445</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5355023668935696</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.533480662983171</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0387341545284835</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7080286116397987</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.182069829617935</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.03745583084112287</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1209063413650723</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2937736264925268</v>
+        <v>-1.455506028246147</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.433181998027912</v>
+        <v>-1.575105791941537</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9971860153251859</v>
+        <v>-0.5333826439555972</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2876268823419142</v>
+        <v>0.08227833917012767</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.02974018915831417</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.302111198606999</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.06507438730253555</v>
+        <v>1.031626818735806</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.30318722338032</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.06203991507733464</v>
+        <v>-1.078920355615719</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.2192196608739769</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WWMKlSMu</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6750438889017567</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.245989055553462</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.228836768199174</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.310825613085734</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.2986212805331784</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.4903481272080951</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.465572143691882</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.2299675209946409</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.4637287206188603</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.4347592902025663</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.2120735657693363</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.9967702106984743</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.01117263445260765</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.4475438888581502</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.3961050278494944</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.2975002707697693</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2093058347037595</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.589971544877438</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1589701170604376</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.9728982485704843</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.4756998695033214</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2099275075646508</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.1070116658143979</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.3300591049427839</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.38522906115678</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-0.2379090544892565</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.7246906815515037</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-0.9723119035627555</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.335879846321268</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.9406682117243637</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.5103359017526544</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.2192196608739769</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>CnIup4yB</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-1.136759031504464</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.245989055553462</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.228836768199174</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.310825613085734</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.939880851273975</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.160313729143112</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8837904666850651</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.3583263600617005</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3815152094324222</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.3105408022721907</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.2120735657693362</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-0.6339830143750272</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.01117263445260765</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.2688811533651317</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.01955875825125977</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.300513803204318</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.2834669622649062</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.9576117151986768</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.739489237705789</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1764180597966731</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.101976820480416</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.100139169560435</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.02534514537450361</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.6745385410518088</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-0.9580696419657933</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.9008134258580049</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.07855482553720022</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.307412256040634</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.2938629833103436</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.1342325955114125</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.09170997189029545</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.2192196608739769</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4MEXoQ6b</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.7215541955780383</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2.245989055553462</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2.228836768199174</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.310825613085734</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.064958564438255</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.4903481272080951</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.465572143691882</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-1.340465962014203</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.9447185368119434</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.3282971356554543</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.5627626384228247</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.7002696243214741</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.01117263445260765</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.3991402519511829</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.7335337809452104</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.6885084131716889</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.9401916424940032</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-1.441231483972464</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.109055708462314</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-0.1109110172951166</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-0.6936981861711818</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.1461571572336632</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.3510071305713063</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.488703574233778</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.5374845789009635</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.3453637146869321</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.5700210546490091</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.038290211304514</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.289798174936723</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-1.558476165098816</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.4334752855733927</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.2192196608739769</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QVFTn6ih</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.4195870421770016</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.245989055553462</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.228836768199174</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.310825613085734</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.4690687611546076</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.179617474726922</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.04735382069869903</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.9048238415441821</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.4572381802620364</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.3815336304827583</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.9134517110763132</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.145020503886975</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.01117263445260765</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.920176646295388</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3961050278494944</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.1105033225853168</v>
-      </c>
-      <c r="R9" t="n">
-        <v>-0.4952248771271269</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.4739919464248913</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.6581142030416746</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-1.260227325662274</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.1505752322735898</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.3212039653141238</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.5609133677505986</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-1.181809128043983</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.3900883831974884</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-0.02086133289594045</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-0.07905925636041149</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.7031898588266356</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.2960315955947846</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-1.141952102294953</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-0.6679058062963121</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.2192196608739769</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>r7QOmnxn</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.6372979947266271</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.245989055553462</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.228836768199174</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.310825613085734</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.9171959675454</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.4903481272080951</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.465572143691882</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.993946607386917</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-2.335046369079947</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.550518329398971</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.877448825457699</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-1.76439149993734</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.9005645832114325</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.140912170476816</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-1.985550127359342</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.275008879849663</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-2.200930811033485</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-1.785810569223786</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.6081997944435511</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.972224791620356</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.4726200918337126</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.179540094558505</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.30349313002975</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.436653242589805</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.7822333639744474</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.04774570553872997</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.06491882450526471</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-2.312713313474268</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.4732836123082279</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.9739988511643626</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.7736896685387932</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.2192196608739769</v>
+        <v>4.561634645420201</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
@@ -425,166 +425,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AV5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -597,37 +672,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.47647207908063</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1345123541393592</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D2" t="n">
-        <v>1.827660902356663</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E2" t="n">
-        <v>3.133458207594984</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.662201125504612</v>
+        <v>1.570684284405742</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.849583076661939</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.370864502294484</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-1.179757309153502</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-1.018059785448941</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0.2386002405046198</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -663,34 +738,79 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5239124094119472</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.5336512952030967</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.5501919728676752</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.369901346229692</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-0.5073471214228522</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.2154898269961419</v>
+        <v>-1.197068098244505</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0.5683113252867548</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.5576836106671057</v>
+        <v>-0.5381528234727851</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.2192196608739769</v>
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.1461757720354481</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.175619748448436</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.09070537845287552</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.1349534906294526</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.332670352041344</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.09140010953732815</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-0.6776083718822182</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-0.6903351341630821</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="3">
@@ -700,37 +820,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9392651481276638</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.635715587450242</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3942362007710887</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E3" t="n">
-        <v>4.855600117935343</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F3" t="n">
-        <v>4.133013215623979</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G3" t="n">
-        <v>2.500244933013146</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H3" t="n">
-        <v>1.720227112671431</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3.781484793578249</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>4.010738775325809</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -766,34 +886,79 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.099518085418156</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.590566165167378</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.4839789641794126</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6377662360768745</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0.3099450631083298</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003268937196141936</v>
+        <v>1.310762565176785</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.643559142272541</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7797032608578869</v>
+        <v>0.8647720645904772</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.2192196608739769</v>
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.513570602589012</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.1093831578336911</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.1392004599075714</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.138653336171462</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.6613509479025669</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.137815933552238</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.826747612047694</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.363665937986686</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="4">
@@ -803,37 +968,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6750438889017567</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>1.158258633612863</v>
+        <v>-1.14364827765869</v>
       </c>
       <c r="D4" t="n">
-        <v>1.117888216635298</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E4" t="n">
-        <v>3.133458207594984</v>
+        <v>0.9993025638977986</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4690687611546076</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.849583076661939</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.370864502294484</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.2347588133950737</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.01728109471056615</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -869,34 +1034,79 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.670424621989281</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.507467294177631</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.514615788485408</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.8785658287791878</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.4987763484521802</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01759428949813836</v>
+        <v>-1.541215809428621</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-1.796382588256907</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.038657077002678</v>
+        <v>-1.199043734333473</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.2192196608739769</v>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.7594485677246998</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.1228330507583776</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.09010594418816957</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.282063465671144</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.9951925175473821</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.9670505483314656</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1.796676474116915</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-2.071352985194133</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="5">
@@ -906,31 +1116,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7215541955780383</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1107601919845012</v>
+        <v>-0.2325249873148829</v>
       </c>
       <c r="D5" t="n">
-        <v>1.889380266332434</v>
+        <v>-0.6815921616005972</v>
       </c>
       <c r="E5" t="n">
-        <v>3.133458207594984</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.150858683640324</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.9435076852138952</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.574342265380581</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -972,34 +1182,79 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.455506028246147</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.575105791941537</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.5333826439555972</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08227833917012767</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-0.6242131872992813</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.031626818735806</v>
+        <v>-2.064364143242678</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-1.910098268084225</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.078920355615719</v>
+        <v>-1.264846255712045</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.561634645420201</v>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.5477829130492949</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.9779613287497709</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.2651075775822376</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.067482418707855</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.01953090607690237</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.6735016759804702</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1.982205839389495</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-1.80700155704934</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.308540478011726</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,23 +668,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4729603000444986</v>
+        <v>-0.09332559573457906</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.410610183269905</v>
+        <v>-1.046101172435251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09518247181964085</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F2" t="n">
-        <v>1.570684284405742</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G2" t="n">
         <v>2.532501625081374</v>
@@ -693,16 +693,16 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.179757309153502</v>
+        <v>-0.9435076852138952</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.018059785448941</v>
+        <v>-0.574342265380581</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2386002405046198</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4576315517288156</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -753,16 +753,16 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5073471214228522</v>
+        <v>0.5520993014240805</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.197068098244505</v>
+        <v>-2.439451353851685</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5683113252867548</v>
+        <v>-1.439532727683684</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.5381528234727851</v>
+        <v>-1.271491883433217</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -771,13 +771,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1461757720354481</v>
+        <v>-1.360535888978865</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.175619748448436</v>
+        <v>0.6725182416976619</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.09070537845287552</v>
+        <v>-0.05387862646966592</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -795,19 +795,19 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.1349534906294526</v>
+        <v>-1.072308374290293</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.332670352041344</v>
+        <v>0.8629730943203149</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.09140010953732815</v>
+        <v>-0.9461446075191189</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.6776083718822182</v>
+        <v>-2.087185343268945</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.6903351341630821</v>
+        <v>-2.29405840323754</v>
       </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
@@ -816,41 +816,41 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.358774610100978</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9222474860718796</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.468191854065507</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3726605901749289</v>
+        <v>1.570684284405742</v>
       </c>
       <c r="G3" t="n">
-        <v>4.256064548547412</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H3" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I3" t="n">
-        <v>3.781484793578249</v>
+        <v>-1.179757309153502</v>
       </c>
       <c r="J3" t="n">
-        <v>4.010738775325809</v>
+        <v>-1.018059785448941</v>
       </c>
       <c r="K3" t="n">
-        <v>2.058814064093999</v>
+        <v>-0.2386002405046198</v>
       </c>
       <c r="L3" t="n">
-        <v>2.032948611842629</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -901,16 +901,16 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.3099450631083298</v>
+        <v>-0.5011058001155981</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.310762565176785</v>
+        <v>-1.223970419192412</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.643559142272541</v>
+        <v>-0.5829300459338373</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.8647720645904772</v>
+        <v>-0.5495033543548912</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -919,13 +919,13 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.513570602589012</v>
+        <v>-0.1492061132814932</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.1093831578336911</v>
+        <v>-0.176180405359852</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.1392004599075714</v>
+        <v>0.08829128664772155</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -943,19 +943,19 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.138653336171462</v>
+        <v>-0.1220187193975283</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6613509479025669</v>
+        <v>1.40766527596645</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.137815933552238</v>
+        <v>-0.08870237166363239</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.826747612047694</v>
+        <v>-0.7029146926355367</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.363665937986686</v>
+        <v>-0.6857498272956946</v>
       </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
@@ -964,41 +964,41 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.14364827765869</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6670911784876219</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9993025638977986</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9498935605813611</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G4" t="n">
-        <v>2.532501625081374</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H4" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2347588133950737</v>
+        <v>3.781484793578249</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01728109471056615</v>
+        <v>4.010738775325809</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.004405008704159</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.4576315517288156</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4987763484521802</v>
+        <v>-0.3099450631083298</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1.541215809428621</v>
+        <v>1.310762565176785</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.796382588256907</v>
+        <v>1.643559142272541</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.199043734333473</v>
+        <v>0.8647720645904772</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.7594485677246998</v>
+        <v>2.513570602589012</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1228330507583776</v>
+        <v>-0.1093831578336911</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.09010594418816957</v>
+        <v>-0.1392004599075714</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.282063465671144</v>
+        <v>1.138653336171462</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.9951925175473821</v>
+        <v>0.6613509479025669</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.9670505483314656</v>
+        <v>4.137815933552238</v>
       </c>
       <c r="AT4" t="n">
-        <v>-1.796676474116915</v>
+        <v>1.826747612047694</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2.071352985194133</v>
+        <v>1.363665937986686</v>
       </c>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
@@ -1112,23 +1112,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2325249873148829</v>
+        <v>-1.14364827765869</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6815921616005972</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1214296335740845</v>
+        <v>0.9993025638977986</v>
       </c>
       <c r="F5" t="n">
-        <v>1.624666086477427</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G5" t="n">
         <v>2.532501625081374</v>
@@ -1137,123 +1137,271 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I5" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4987763484521802</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.541215809428621</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1.796382588256907</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1.199043734333474</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.7594485677246998</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.1228330507583776</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.09010594418816957</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.282063465671144</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.9951925175473821</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.9670505483314656</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1.796676474116915</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-2.071352985194133</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2325249873148829</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.6815921616005972</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1214296335740845</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.624666086477427</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I6" t="n">
         <v>-0.9435076852138952</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>-0.574342265380581</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-0.6242131872992813</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-2.064364143242678</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.910098268084225</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.6279126760667447</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.081539284903858</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1.899539817707468</v>
+      </c>
+      <c r="AF6" t="n">
         <v>-1.264846255712045</v>
       </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-0.5477829130492949</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.9779613287497709</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.2651075775822376</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.548662245279546</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9993982106568647</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2581079899897578</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>-1.067482418707855</v>
       </c>
-      <c r="AR5" t="n">
-        <v>0.01953090607690237</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.6735016759804702</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-1.982205839389495</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-1.80700155704934</v>
-      </c>
-      <c r="AV5" t="n">
+      <c r="AR6" t="n">
+        <v>0.04696377204612421</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.6717368466425522</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-1.9651034515757</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-1.809308767884735</v>
+      </c>
+      <c r="AV6" t="n">
         <v>5.308540478011726</v>
       </c>
     </row>

--- a/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_selected_nan.xlsx
@@ -753,16 +753,16 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5520993014240805</v>
+        <v>0.8455523018335774</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2.439451353851685</v>
+        <v>-2.447643452342835</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.439532727683684</v>
+        <v>-1.252955061685929</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.271491883433217</v>
+        <v>-1.029172219982066</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -771,13 +771,13 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.360535888978865</v>
+        <v>-1.383011493221171</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.6725182416976619</v>
+        <v>0.6287902387221393</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.05387862646966592</v>
+        <v>-0.5346190325260441</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -795,19 +795,19 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.072308374290293</v>
+        <v>-1.062031876845381</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8629730943203149</v>
+        <v>0.7585517458221516</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.9461446075191189</v>
+        <v>-0.7953548134718232</v>
       </c>
       <c r="AT2" t="n">
-        <v>-2.087185343268945</v>
+        <v>-2.146130072729493</v>
       </c>
       <c r="AU2" t="n">
-        <v>-2.29405840323754</v>
+        <v>-2.317802445329099</v>
       </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
@@ -901,16 +901,16 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.5011058001155981</v>
+        <v>-0.2574838419377251</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.223970419192412</v>
+        <v>-1.207810663264663</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.5829300459338373</v>
+        <v>-0.5368080399575579</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.5495033543548912</v>
+        <v>-0.5895666947753213</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -919,13 +919,13 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1492061132814932</v>
+        <v>-0.1503557522000063</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.176180405359852</v>
+        <v>-0.3989675015189203</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.08829128664772155</v>
+        <v>0.1636491408876873</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -943,19 +943,19 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.1220187193975283</v>
+        <v>-0.1305770642727867</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.40766527596645</v>
+        <v>1.408274397561845</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.08870237166363239</v>
+        <v>-0.09856729195274005</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.7029146926355367</v>
+        <v>-0.8554169196741922</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.6857498272956946</v>
+        <v>-0.6784496238687691</v>
       </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
@@ -1049,16 +1049,16 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.3099450631083298</v>
+        <v>-0.6046397244207872</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.310762565176785</v>
+        <v>1.185528293335922</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.643559142272541</v>
+        <v>2.000671248197561</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.8647720645904772</v>
+        <v>1.236534809994035</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1067,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.513570602589012</v>
+        <v>2.023383215046395</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1093831578336911</v>
+        <v>0.2742514443983327</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.1392004599075714</v>
+        <v>-0.3223804881868177</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1091,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.138653336171462</v>
+        <v>0.9492107555832001</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6613509479025669</v>
+        <v>0.7271026980668596</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.137815933552238</v>
+        <v>5.726817186723991</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.826747612047694</v>
+        <v>2.261424701179745</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.363665937986686</v>
+        <v>1.257081257060226</v>
       </c>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.4987763484521802</v>
+        <v>0.3875367961142823</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.541215809428621</v>
+        <v>-1.509756752109526</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.796382588256907</v>
+        <v>-1.69054836818864</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.199043734333474</v>
+        <v>-1.101313955924437</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1215,13 +1215,13 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.7594485677246998</v>
+        <v>-0.7258008289145049</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1228330507583776</v>
+        <v>0.01256923397797134</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.09010594418816957</v>
+        <v>-0.2008114170056553</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1239,19 +1239,19 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.282063465671144</v>
+        <v>-1.254832368340777</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.9951925175473821</v>
+        <v>-0.9662846218324346</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.9670505483314656</v>
+        <v>-0.8549355163277714</v>
       </c>
       <c r="AT5" t="n">
-        <v>-1.796676474116915</v>
+        <v>-1.772725364297222</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2.071352985194133</v>
+        <v>-2.090889567610786</v>
       </c>
       <c r="AV5" t="n">
         <v>-0.1883756946268106</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6279126760667447</v>
+        <v>-0.875453107318633</v>
       </c>
       <c r="AD6" t="n">
-        <v>-2.081539284903858</v>
+        <v>-2.178252975683592</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.899539817707468</v>
+        <v>-1.962803158575299</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.264846255712045</v>
+        <v>-1.318078721308519</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1363,13 +1363,13 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.548662245279546</v>
+        <v>-0.5551805107969936</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.9993982106568647</v>
+        <v>1.260868206617462</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.2581079899897578</v>
+        <v>-0.6733971379630761</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1387,19 +1387,19 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.067482418707855</v>
+        <v>-1.023368041032661</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.04696377204612421</v>
+        <v>0.2866869599239795</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.6717368466425522</v>
+        <v>-0.6882651275083299</v>
       </c>
       <c r="AT6" t="n">
-        <v>-1.9651034515757</v>
+        <v>-1.894469010631035</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.809308767884735</v>
+        <v>-1.780719862066613</v>
       </c>
       <c r="AV6" t="n">
         <v>5.308540478011726</v>
